--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260623.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260623.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>14.50%</t>
+          <t>14.51%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>13.28%</t>
+          <t>13.45%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>11.77%</t>
+          <t>11.63%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>11.08%</t>
+          <t>11.46%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>6.53%</t>
+          <t>6.60%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.79%</t>
+          <t>4.81%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>39,275,000</t>
+          <t>38,395,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.99%</t>
+          <t>3.77%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.56%</t>
+          <t>3.44%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.42%</t>
+          <t>3.38%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.92%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.62%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.57%</t>
         </is>
       </c>
     </row>
@@ -902,51 +902,51 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.48%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>64,710,000</t>
+          <t>205,760,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>205,760,000</t>
+          <t>64,710,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>71,639,000</t>
+          <t>71,319,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.72%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.70%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.67%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.62%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.56%</t>
         </is>
       </c>
     </row>
@@ -1217,83 +1217,83 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>義隆</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>15,330,000</t>
+          <t>34,100,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>9910</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>豐泰</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>26,819,000</t>
+          <t>36,440,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>34,100,000</t>
+          <t>26,819,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>豐泰</t>
+          <t>義隆</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>36,440,000</t>
+          <t>15,330,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,39 +1305,39 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>9941</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>裕融</t>
+          <t>潤弘</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>29,940,000</t>
+          <t>14,190,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2597</t>
+          <t>9941</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>潤弘</t>
+          <t>裕融</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>14,190,000</t>
+          <t>29,940,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1371,66 +1371,66 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>27,850,000</t>
+          <t>7,990,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>7,990,000</t>
+          <t>41,370,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>41,370,000</t>
+          <t>27,850,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.39%</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>3,222,824,749</t>
+          <t>4,390,367,777</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr"/>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>2,884,593,186</t>
+          <t>2,781,529,186</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr"/>
@@ -3043,7 +3043,7 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>-1,889,065,557</t>
+          <t>-2,592,561,059</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr"/>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>1,529,706,159</t>
+          <t>773,449,700</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr"/>
